--- a/vtcourts_results.xlsx
+++ b/vtcourts_results.xlsx
@@ -431,14 +431,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="43" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="36" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -457,16 +455,6 @@
           <t>Location</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Searched Name</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Date Added</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -484,16 +472,6 @@
           <t>Windsor Unit</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>J.G. Wentworth Originations, LLC</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>06/25/2026</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -511,16 +489,6 @@
           <t>Windsor Unit</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>J.G. Wentworth Originations, LLC</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>06/25/2026</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -538,16 +506,6 @@
           <t>Windsor Unit</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>J.G. Wentworth Originations, LLC</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>06/25/2026</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -565,16 +523,6 @@
           <t>Caledonia Unit</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>J.G. Wentworth Originations, LLC</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>06/25/2026</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -592,16 +540,6 @@
           <t>Chittenden Unit</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>J.G. Wentworth Originations, LLC</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>06/25/2026</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -617,16 +555,6 @@
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>Windsor Unit</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>J. G. Wentworth Originations LLC</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>06/25/2026</t>
         </is>
       </c>
     </row>
